--- a/Template_RADAR_Gizi.xlsx
+++ b/Template_RADAR_Gizi.xlsx
@@ -469,7 +469,7 @@
     <t xml:space="preserve">RADAR Gizi (Rekap Analisis Determinan dan Area Rawan Gizi), pendamping e-PPGBM untuk menentukan desa prioritas intervensi gizi</t>
   </si>
   <si>
-    <t xml:space="preserve">Dikembangkan oleh Manjilala, Poltekkes Kemenkes Makassar</t>
+    <t xml:space="preserve">Aplikasi dikembangkan oleh: Ainun Thahirah H., Aminah Razaq dan Andi Marhamatul Ginayah | Mahasiswa Prodi Gizi dan Dietetika Poltekkes Kemenkes Makassar. Dibimbing oleh Manjilala, S.Gz, M.Gizi dan Dr. Nadimin, SKM, M.Kes</t>
   </si>
   <si>
     <t xml:space="preserve">Cara pengisian</t>
